--- a/pacjenci/KAROLINA RADWAŃSKA.xlsx
+++ b/pacjenci/KAROLINA RADWAŃSKA.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -534,7 +534,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G3" t="n">

--- a/pacjenci/KAROLINA RADWAŃSKA.xlsx
+++ b/pacjenci/KAROLINA RADWAŃSKA.xlsx
@@ -413,191 +413,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>29.11.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina - ocena zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  61min od podania 18F-FDG. Glikemia: 79mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Węzeł chłonny nadobojczykowy prawy wielkości 10mm, SUV max 3,4. Pobudzony metabolicznie, częściowo uwapniony obszar wielkości 9mm, SUV max 4,1 w lewej zatoce szczękowej, w obrębie masywnej zmiany polipowatej [wielkości 21x18mm] - infekcja grzybicza? inne - celowa konsultacja laryngologiczna. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Tarczyca powiększona, o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Aktywna metabolicznie masa miękkotkankowa w śródpiersiu przednim i środkowym po stronie prawej wielkości 37x31x72mm wg PET, SUV max do 13,2. Pojedyncze izolujące się węzły chłonne w śródpiersiu po stronie prawej wielkości do 16mm wg PET, SUV max do 7,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc.  Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Pobudzenie metaboliczne w topografii endometrium i jamy macicy oraz w topografii szyjki macicy, SUV max do 8,8 - związane z fazą cyklu? Rozlanie wzmożony metabolizm FDG w topografii pętli jelita cienkiego położonych w miednicy obustronnie, SUV max do 11,5. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie prawej.  Układ kostny: Zwiększona aktywność metaboliczna w lewobocznej części łuku kręgu Th6, SUV max 12,8 - do weryfikacji w badaniu MR z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowe kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym segmencie kręgosłupa piersiowego. Dwuwklęsłe obrysy trzonów kręgowych w dolnym segmencie kręgosłupa lędźwiowego. Os sacrum arcuatum.  Inne: Mierne pobudzenie metaboliczne w tkance brunatnej szyi.  Pobudzenie metaboliczne w tkankach miękkich stawów barkowych obustronnie- zmiany przeciążeniowe?  Wartości referencyjne: MBPS SUVmax do 1,7; Prawy płat wątroby SUVmax do 2,9.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego po jednej stronie przepony z niewykluczonym objęciem pojedynczego kręgu - do weryfikacji. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>13.2</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>17.03.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina - ocena wczesnej odpowiedzi po 2 cyklach ChTh.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 77mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Symetrycznie wzmożony metabolizm FDG w wyraźnie powiększonych strukturach pierścienia Waldeyera, SUV max do 12,1 - do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Częściowo uwapniony obszar wielkości 9mm,  w lewej zatoce szczękowej, w obrębie wydatniejszej  polipowatej zmiany [wielkości 21x18mm] - infekcja grzybicza? inne - celowa konsultacja laryngologiczna. Drobny pooperacyjny ubytek ściany przyśrodkowej lewej zatoki szczękowej. Tarczyca powiększona, o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny przytchawiczy górny prawy wielkości 12x8 mm  SUVmax 4,8- w tej okolicy widoczne są drobniejsze klipsy pozabiegowe.  Miernie pobudzone metabolicznie masy miękkotkankowe w obrębie przedniej i środkowej części śródpiersia górnego - pośrodkowo i po stronie prawej wielkości do 28x33 mm SUVmax do 1,9 [w okolicy klipsów naczyniowych]. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc.  Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Pobudzenie metaboliczne w topografii endometrium i jamy macicy, SUV max do 3,2  - zmiany mogą być związane z fazą cyklu (OM 08.03.2022).   Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie prawej - jak poprzednio.   Układ kostny: Aktywny metabolicznie obszar w lewobocznej części łuku kręgu Th6, SUV max 16,2, z widocznym drobnym litycznym ubytkiem struktury kostnej. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowe kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym segmencie kręgosłupa piersiowego. Dwuwklęsłe obrysy trzonów kręgowych w dolnym segmencie kręgosłupa lędźwiowego. Niewielka dyskopatia, z nierównym obrysem blaszek granicznych trzonów kręgowych na poziomie L5/S1. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 3,0.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie procesu chłoniakowego - w porównaniu do badania poprzedniego PET,  z dnia 29.11.2021 widoczny jest nowy aktywny metabolicznie węzeł chłonny przytchawiczy górny prawy oraz utrzymujące się aktywne metabolicznie ognisko w topografii lewobocznej części łuku kręgu Th6. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>16.2</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>17.05.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Badanie kontrolne.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 85 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Symetrycznie wzmożony metabolizm FDG w wyraźnie powiększonych strukturach pierścienia Waldeyera, SUV max do 4,0. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aktualnie przyścienne zgrubienia błony śluzowej oraz ok. 13mm polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej. Drobny pooperacyjny ubytek ściany przyśrodkowej lewej zatoki szczękowej. Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masy miękkotkankowe w obrębie przedniej i środkowej części śródpiersia górnego - pośrodkowo i po stronie prawej wielkości do 27x34 mm [Im CT 279]. Drobne zmiany włókniste w szczytach obu płuc.  Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie prawej - jak poprzednio.   Układ kostny: Aktywny metabolicznie obszar w lewobocznej części łuku kręgu Th6 średnicy 9 mm SUV max 9,0, z widocznym drobnym litycznym ubytkiem struktury kostnej. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowe kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym segmencie kręgosłupa piersiowego. Dwuwklęsłe obrysy trzonów kręgowych w dolnym segmencie kręgosłupa lędźwiowego. Niewielka dyskopatia, z nierównym obrysem blaszek granicznych trzonów kręgowych na poziomie L5/S1. Os sacrum arcuatum.  Inne: Ogniskowo wzmożony metabolizm FDG w topografii skóry i tkanki podskórnej w górnej części pleców po stronie lewej SUV max 2,1 [Im fuz. 83] - zmiana  zapalna?- do kontroli miejscowej.  Wartości referencyjne: MBPS SUVmax do 1,1; Prawy płat wątroby SUVmax do 1,7.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie obszaru w topografii lewobocznej części łuku kręgu Th6.  Poza tym jak w opisie powyżej.   18,07,022 Zakres badania: od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 96 mg%. Problem kliniczny:  Chłoniak Hodgkina. Ocena remisji choroby po zakończeniu chemioterapiii.   Konsultujący specjalista Radiologii i Diagnostyki Obrazowej: Dr n. med. Agata Brzozowska-Czarnek  Głowa i szyja: Zwiększony metabolizm FDG w strukturach pierścienia Waldeyera- czynnościowo? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 15x11mm. Drobny pooperacyjny ubytek ściany przyśrodkowej lewej zatoki szczękowej. Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK.  Klatka piersiowa i śródpiersie: Niejednoznaczny aktywny metabolicznie obszar na pograniczu dolnej części szyi i śródpiersia górnego, nieco na prawo od linii środkowej ciała, wielkości ok.  12x14mm wg PET, SUV max 4,0 - do ew. weryfikacji w badaniu TK/MR z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masy miękkotkankowe w obrębie przedniej i środkowej części śródpiersia górnego - pośrodkowo i po stronie prawej wielkości do 22x29 mm. Drobne zmiany włókniste w szczytach obu płuc.  Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie prawej - jak poprzednio.   Układ kostny: Nadal widoczny jest aktywny metabolicznie obszar w lewobocznej części łuku kręgu Th6 średnicy 12 mm wg PET, SUV max 8,5, z widocznym niewielkim litycznym ubytkiem struktury kostnej. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowe kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym segmencie kręgosłupa piersiowego. Dwuwklęsłe obrysy trzonów kręgowych w dolnym segmencie kręgosłupa lędźwiowego. Niewielka dyskopatia, z nierównym obrysem blaszek granicznych trzonów kręgowych na poziomie L5/S1. Os sacrum arcuatum.  Inne: Zwiększony metabolizm FDG w strukturach mięśniowych karku obustronnie -zmiany przeciążeniowe?  Wartości referencyjne: MBPS SUVmax do 2,2; Prawy płat wątroby SUVmax do 3,3.  Wnioski: Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie obszaru w topografii lewobocznej części łuku kręgu Th6.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>9</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/KAROLINA RADWAŃSKA.xlsx
+++ b/pacjenci/KAROLINA RADWAŃSKA.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po  61min od podania 18F-FDG. Glikemia: 79mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Węzeł chłonny nadobojczykowy prawy wielkości 10mm, SUV max 3,4. Pobudzony metabolicznie, częściowo uwapniony obszar wielkości 9mm, SUV max 4,1 w lewej zatoce szczękowej, w obrębie masywnej zmiany polipowatej [wielkości 21x18mm] - infekcja grzybicza? inne - celowa konsultacja laryngologiczna. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Tarczyca powiększona, o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Aktywna metabolicznie masa miękkotkankowa w śródpiersiu przednim i środkowym po stronie prawej wielkości 37x31x72mm wg PET, SUV max do 13,2. Pojedyncze izolujące się węzły chłonne w śródpiersiu po stronie prawej wielkości do 16mm wg PET, SUV max do 7,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc.  Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Pobudzenie metaboliczne w topografii endometrium i jamy macicy oraz w topografii szyjki macicy, SUV max do 8,8 - związane z fazą cyklu? Rozlanie wzmożony metabolizm FDG w topografii pętli jelita cienkiego położonych w miednicy obustronnie, SUV max do 11,5. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie prawej.  Układ kostny: Zwiększona aktywność metaboliczna w lewobocznej części łuku kręgu Th6, SUV max 12,8 - do weryfikacji w badaniu MR z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowe kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym segmencie kręgosłupa piersiowego. Dwuwklęsłe obrysy trzonów kręgowych w dolnym segmencie kręgosłupa lędźwiowego. Os sacrum arcuatum.  Inne: Mierne pobudzenie metaboliczne w tkance brunatnej szyi.  Pobudzenie metaboliczne w tkankach miękkich stawów barkowych obustronnie- zmiany przeciążeniowe?  Wartości referencyjne: MBPS SUVmax do 1,7; Prawy płat wątroby SUVmax do 2,9.</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Węzeł chłonny nadobojczykowy prawy wielkości 10mm, SUV max 3,4. Pobudzony metabolicznie, częściowo uwapniony obszar wielkości 9mm, SUV max 4,1 w lewej zatoce szczękowej, w obrębie masywnej zmiany polipowatej [wielkości 21x18mm] - infekcja grzybicza? inne - celowa konsultacja laryngologiczna. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Tarczyca powiększona, o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywna metabolicznie masa miękkotkankowa w śródpiersiu przednim i środkowym po stronie prawej wielkości 37x31x72mm wg PET, SUV max do 13,2. Pojedyncze izolujące się węzły chłonne w śródpiersiu po stronie prawej wielkości do 16mm wg PET, SUV max do 7,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc.  Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w topografii endometrium i jamy macicy oraz w topografii szyjki macicy, SUV max do 8,8 - związane z fazą cyklu? Rozlanie wzmożony metabolizm FDG w topografii pętli jelita cienkiego położonych w miednicy obustronnie, SUV max do 11,5. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Zwiększona aktywność metaboliczna w lewobocznej części łuku kręgu Th6, SUV max 12,8 - do weryfikacji w badaniu MR z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowe kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym segmencie kręgosłupa piersiowego. Dwuwklęsłe obrysy trzonów kręgowych w dolnym segmencie kręgosłupa lędźwiowego. Os sacrum arcuatum.  Inne: Mierne pobudzenie metaboliczne w tkance brunatnej szyi.  Pobudzenie metaboliczne w tkankach miękkich stawów barkowych obustronnie- zmiany przeciążeniowe?</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego po jednej stronie przepony z niewykluczonym objęciem pojedynczego kręgu - do weryfikacji. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>13.2</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 77mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Symetrycznie wzmożony metabolizm FDG w wyraźnie powiększonych strukturach pierścienia Waldeyera, SUV max do 12,1 - do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Częściowo uwapniony obszar wielkości 9mm,  w lewej zatoce szczękowej, w obrębie wydatniejszej  polipowatej zmiany [wielkości 21x18mm] - infekcja grzybicza? inne - celowa konsultacja laryngologiczna. Drobny pooperacyjny ubytek ściany przyśrodkowej lewej zatoki szczękowej. Tarczyca powiększona, o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Aktywny metabolicznie węzeł chłonny przytchawiczy górny prawy wielkości 12x8 mm  SUVmax 4,8- w tej okolicy widoczne są drobniejsze klipsy pozabiegowe.  Miernie pobudzone metabolicznie masy miękkotkankowe w obrębie przedniej i środkowej części śródpiersia górnego - pośrodkowo i po stronie prawej wielkości do 28x33 mm SUVmax do 1,9 [w okolicy klipsów naczyniowych]. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc.  Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Pobudzenie metaboliczne w topografii endometrium i jamy macicy, SUV max do 3,2  - zmiany mogą być związane z fazą cyklu (OM 08.03.2022).   Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie prawej - jak poprzednio.   Układ kostny: Aktywny metabolicznie obszar w lewobocznej części łuku kręgu Th6, SUV max 16,2, z widocznym drobnym litycznym ubytkiem struktury kostnej. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowe kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym segmencie kręgosłupa piersiowego. Dwuwklęsłe obrysy trzonów kręgowych w dolnym segmencie kręgosłupa lędźwiowego. Niewielka dyskopatia, z nierównym obrysem blaszek granicznych trzonów kręgowych na poziomie L5/S1. Os sacrum arcuatum.  Wartości referencyjne: MBPS SUVmax do 1,8; Prawy płat wątroby SUVmax do 3,0.</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Symetrycznie wzmożony metabolizm FDG w wyraźnie powiększonych strukturach pierścienia Waldeyera, SUV max do 12,1 - do ew. kontroli laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Częściowo uwapniony obszar wielkości 9mm,  w lewej zatoce szczękowej, w obrębie wydatniejszej  polipowatej zmiany [wielkości 21x18mm] - infekcja grzybicza? inne - celowa konsultacja laryngologiczna. Drobny pooperacyjny ubytek ściany przyśrodkowej lewej zatoki szczękowej. Tarczyca powiększona, o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie węzeł chłonny przytchawiczy górny prawy wielkości 12x8 mm  SUVmax 4,8- w tej okolicy widoczne są drobniejsze klipsy pozabiegowe.  Miernie pobudzone metabolicznie masy miękkotkankowe w obrębie przedniej i środkowej części śródpiersia górnego - pośrodkowo i po stronie prawej wielkości do 28x33 mm SUVmax do 1,9 [w okolicy klipsów naczyniowych]. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc.  Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w topografii endometrium i jamy macicy, SUV max do 3,2  - zmiany mogą być związane z fazą cyklu (OM 08.03.2022).   Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie prawej - jak poprzednio.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w lewobocznej części łuku kręgu Th6, SUV max 16,2, z widocznym drobnym litycznym ubytkiem struktury kostnej. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowe kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym segmencie kręgosłupa piersiowego. Dwuwklęsłe obrysy trzonów kręgowych w dolnym segmencie kręgosłupa lędźwiowego. Niewielka dyskopatia, z nierównym obrysem blaszek granicznych trzonów kręgowych na poziomie L5/S1. Os sacrum arcuatum.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie procesu chłoniakowego - w porównaniu do badania poprzedniego PET,  z dnia 29.11.2021 widoczny jest nowy aktywny metabolicznie węzeł chłonny przytchawiczy górny prawy oraz utrzymujące się aktywne metabolicznie ognisko w topografii lewobocznej części łuku kręgu Th6. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>16.2</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 85 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Symetrycznie wzmożony metabolizm FDG w wyraźnie powiększonych strukturach pierścienia Waldeyera, SUV max do 4,0. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aktualnie przyścienne zgrubienia błony śluzowej oraz ok. 13mm polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej. Drobny pooperacyjny ubytek ściany przyśrodkowej lewej zatoki szczękowej. Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masy miękkotkankowe w obrębie przedniej i środkowej części śródpiersia górnego - pośrodkowo i po stronie prawej wielkości do 27x34 mm [Im CT 279]. Drobne zmiany włókniste w szczytach obu płuc.  Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie prawej - jak poprzednio.   Układ kostny: Aktywny metabolicznie obszar w lewobocznej części łuku kręgu Th6 średnicy 9 mm SUV max 9,0, z widocznym drobnym litycznym ubytkiem struktury kostnej. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowe kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym segmencie kręgosłupa piersiowego. Dwuwklęsłe obrysy trzonów kręgowych w dolnym segmencie kręgosłupa lędźwiowego. Niewielka dyskopatia, z nierównym obrysem blaszek granicznych trzonów kręgowych na poziomie L5/S1. Os sacrum arcuatum.  Inne: Ogniskowo wzmożony metabolizm FDG w topografii skóry i tkanki podskórnej w górnej części pleców po stronie lewej SUV max 2,1 [Im fuz. 83] - zmiana  zapalna?- do kontroli miejscowej.  Wartości referencyjne: MBPS SUVmax do 1,1; Prawy płat wątroby SUVmax do 1,7.</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Symetrycznie wzmożony metabolizm FDG w wyraźnie powiększonych strukturach pierścienia Waldeyera, SUV max do 4,0. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Aktualnie przyścienne zgrubienia błony śluzowej oraz ok. 13mm polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej. Drobny pooperacyjny ubytek ściany przyśrodkowej lewej zatoki szczękowej. Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK - do kontroli w USG.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masy miękkotkankowe w obrębie przedniej i środkowej części śródpiersia górnego - pośrodkowo i po stronie prawej wielkości do 27x34 mm [Im CT 279]. Drobne zmiany włókniste w szczytach obu płuc.  Niewielkie zmiany włókniste obustronnie nadprzeponowo.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie prawej - jak poprzednio.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w lewobocznej części łuku kręgu Th6 średnicy 9 mm SUV max 9,0, z widocznym drobnym litycznym ubytkiem struktury kostnej. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowe kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym segmencie kręgosłupa piersiowego. Dwuwklęsłe obrysy trzonów kręgowych w dolnym segmencie kręgosłupa lędźwiowego. Niewielka dyskopatia, z nierównym obrysem blaszek granicznych trzonów kręgowych na poziomie L5/S1. Os sacrum arcuatum.  Inne: Ogniskowo wzmożony metabolizm FDG w topografii skóry i tkanki podskórnej w górnej części pleców po stronie lewej SUV max 2,1 [Im fuz. 83] - zmiana  zapalna?- do kontroli miejscowej.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie obszaru w topografii lewobocznej części łuku kręgu Th6.  Poza tym jak w opisie powyżej.   18,07,022 Zakres badania: od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 96 mg%. Problem kliniczny:  Chłoniak Hodgkina. Ocena remisji choroby po zakończeniu chemioterapiii.   Konsultujący specjalista Radiologii i Diagnostyki Obrazowej: Dr n. med. Agata Brzozowska-Czarnek  Głowa i szyja: Zwiększony metabolizm FDG w strukturach pierścienia Waldeyera- czynnościowo? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienie błony śluzowej w lewej zatoce szczękowej, wielkości 15x11mm. Drobny pooperacyjny ubytek ściany przyśrodkowej lewej zatoki szczękowej. Tarczyca o niejednorodnym cieniowaniu w przeglądowym badaniu TK.  Klatka piersiowa i śródpiersie: Niejednoznaczny aktywny metabolicznie obszar na pograniczu dolnej części szyi i śródpiersia górnego, nieco na prawo od linii środkowej ciała, wielkości ok.  12x14mm wg PET, SUV max 4,0 - do ew. weryfikacji w badaniu TK/MR z kontrastem dożylnym. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Masy miękkotkankowe w obrębie przedniej i środkowej części śródpiersia górnego - pośrodkowo i po stronie prawej wielkości do 22x29 mm. Drobne zmiany włókniste w szczytach obu płuc.  Niewielkie zmiany włókniste obustronnie nadprzeponowo.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie prawej - jak poprzednio.   Układ kostny: Nadal widoczny jest aktywny metabolicznie obszar w lewobocznej części łuku kręgu Th6 średnicy 12 mm wg PET, SUV max 8,5, z widocznym niewielkim litycznym ubytkiem struktury kostnej. Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Niewielkie zmiany zwyrodnieniowe kręgosłupa. Nierówne obrysy blaszek granicznych trzonów kręgowych w dolnym segmencie kręgosłupa piersiowego. Dwuwklęsłe obrysy trzonów kręgowych w dolnym segmencie kręgosłupa lędźwiowego. Niewielka dyskopatia, z nierównym obrysem blaszek granicznych trzonów kręgowych na poziomie L5/S1. Os sacrum arcuatum.  Inne: Zwiększony metabolizm FDG w strukturach mięśniowych karku obustronnie -zmiany przeciążeniowe?  Wartości referencyjne: MBPS SUVmax do 2,2; Prawy płat wątroby SUVmax do 3,3.  Wnioski: Badaniem PET/CT z 18F-FDG uwidoczniono obecność nadal aktywnego metabolicznie obszaru w topografii lewobocznej części łuku kręgu Th6.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>9</v>
       </c>
     </row>
